--- a/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la cuisine avec maman. Il empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Hugo sent son visage brûler. Ses mains deviennent chaudes et dures. Hugo dit : je suis en colère. Il ouvre les doigts. Il garde les mains loin. Hugo peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement. Hugo dit : maman, je suis en colère. La tour est tombée. Maman écoute. Hugo reste près d'elle. Plus tard, ils vont au jardin. Hugo arrose les fleurs. Un camarade renverse l'arrosoir. L'eau part. Hugo sent encore la chaleur. Il se souvient. Il dit : je suis en colère. Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle. Maman dit : tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Hugo est dans la cuisine avec maman. Il empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Hugo sent son visage brûler. Ses mains deviennent chaudes et dures. Je suis en colère. Il ouvre les doigts. Il garde les mains loin. Hugo peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement. Maman, je suis en colère. La tour est tombée. Maman écoute. Hugo reste près d'elle. Plus tard, ils vont au jardin. Hugo arrose les fleurs. Un camarade renverse l'arrosoir. L'eau part. Hugo sent encore la chaleur. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans la cuisine avec maman. Il empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Hugo sent son visage brûler. Ses mains deviennent chaudes et dures.
+enfant-m|Je suis en colère. Il ouvre les doigts. Il garde les mains loin.
+narrateur|Hugo peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement.
+enfant-m|Maman, je suis en colère.
+narrateur|La tour est tombée. Maman écoute. Hugo reste près d'elle. Plus tard, ils vont au jardin. Hugo arrose les fleurs. Un camarade renverse l'arrosoir. L'eau part. Hugo sent encore la chaleur. Il se souvient.
+narrateur|Je suis en colère.
+narrateur|Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle.
+maman|Tu as nommé. Tu as repris le geste. Même leçon, autre lieu.
+narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La tour de Hugo s'affaisse. Que fait-il de sa colère ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo repose un cube. Maman reste près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|La tour de Hugo s'affaisse. Que fait-il de sa colère ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Hugo repose un cube. Maman reste près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hugo nomme sa colère deux fois</t>
+          <t>Aniss nomme sa colère deux fois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La tour d'Aniss s'affaisse, puis l'arrosoir se renverse. Deux fois, il nomme, mains loin, s'éloigne, rejoint maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans la cuisine avec maman. Il empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Hugo sent son visage brûler. Ses mains deviennent chaudes et dures. Je suis en colère. Il ouvre les doigts. Il garde les mains loin. Hugo peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement. Maman, je suis en colère. La tour est tombée. Maman écoute. Hugo reste près d'elle. Plus tard, ils vont au jardin. Hugo arrose les fleurs. Un camarade renverse l'arrosoir. L'eau part. Hugo sent encore la chaleur. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Un cube en bois sent le pin. La porte du jardin est ouverte. Un zeste de citron brille sur la table. Maman essuie une miette. Une abeille passe devant la porte. Le carrelage est un peu froid. Les cubes sont près du saladier. Aniss, tu empiles tout doux ? Oui. Une tour haute. En ce moment, Aniss empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Aniss sent son visage brûler. Ses mains deviennent chaudes. Je suis en colère. Il ouvre les doigts. Il garde les mains loin. Les mains restent loin. Aniss peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement. Maman, je suis en colère. Je t'écoute. La tour est tombée. Tu as nommé. Bravo. Aniss reste près d'elle. Plus tard, ils vont au jardin. Aniss arrose les fleurs. Victorino passe près des pots. L'arrosoir se renverse. L'eau part. Aniss sent encore la chaleur. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle. Tu as nommé. Tu as soufflé encore. Au jardin, tu as fait pareil. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte. Tu as soufflé à la table. Tu as soufflé au jardin. Deux fois. Mains loin. L'eau brille sur les dalles. Le citron sent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est dans la cuisine avec maman. Il empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Hugo sent son visage brûler. Ses mains deviennent chaudes et dures.
-enfant-m|Je suis en colère. Il ouvre les doigts. Il garde les mains loin.
-narrateur|Hugo peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement.
+          <t>narrateur|Un cube en bois sent le pin.
+narrateur|La porte du jardin est ouverte.
+narrateur|Un zeste de citron brille sur la table.
+narrateur|Maman essuie une miette.
+narrateur|Une abeille passe devant la porte.
+narrateur|Le carrelage est un peu froid.
+papa|Les cubes sont près du saladier.
+maman|Aniss, tu empiles tout doux ?
+enfant-m|Oui. Une tour haute.
+narrateur|En ce moment, Aniss empile des cubes.
+narrateur|La tour est haute.
+narrateur|Un cube glisse.
+narrateur|La tour s'affaisse.
+narrateur|Aniss sent son visage brûler.
+narrateur|Ses mains deviennent chaudes.
+enfant-m|Je suis en colère.
+narrateur|Il ouvre les doigts.
+narrateur|Il garde les mains loin.
+maman|Les mains restent loin.
+narrateur|Aniss peut s'éloigner.
+narrateur|Il s'éloigne de la table.
+narrateur|Il va près de maman.
+narrateur|Il souffle quatre fois, lentement.
 enfant-m|Maman, je suis en colère.
-narrateur|La tour est tombée. Maman écoute. Hugo reste près d'elle. Plus tard, ils vont au jardin. Hugo arrose les fleurs. Un camarade renverse l'arrosoir. L'eau part. Hugo sent encore la chaleur. Il se souvient.
-narrateur|Je suis en colère.
-narrateur|Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle.
-maman|Tu as nommé. Tu as repris le geste. Même leçon, autre lieu.
-narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Je t'écoute.
+enfant-m|La tour est tombée.
+papa|Tu as nommé. Bravo.
+narrateur|Aniss reste près d'elle.
+narrateur|Plus tard, ils vont au jardin.
+narrateur|Aniss arrose les fleurs.
+narrateur|Victorino passe près des pots.
+narrateur|L'arrosoir se renverse.
+narrateur|L'eau part.
+narrateur|Aniss sent encore la chaleur.
+narrateur|Il se souvient.
+enfant-m|Je suis en colère.
+narrateur|Les mains restent loin.
+narrateur|Il s'éloigne.
+narrateur|Il va vers maman, l'adulte.
+narrateur|Il souffle.
+maman|Tu as nommé. Tu as soufflé encore.
+papa|Au jardin, tu as fait pareil.
+narrateur|La colère a un nom.
+narrateur|Les mains restent loin.
+narrateur|On s'éloigne.
+narrateur|On va vers un adulte.
+papa|Tu as soufflé à la table.
+maman|Tu as soufflé au jardin.
+enfant-m|Deux fois. Mains loin.
+narrateur|L'eau brille sur les dalles.
+narrateur|Le citron sent encore.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine,jardin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La tour de Hugo s'affaisse. Que fait-il de sa colère ?</t>
+          <t>La tour d'Aniss s'affaisse. Que fait-il de sa colère ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1566,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La tour de Hugo s'affaisse. Que fait-il de sa colère ?</t>
+          <t>narrateur|La tour d'Aniss s'affaisse.
+narrateur|Que fait-il de sa colère ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois.</t>
+          <t>Aniss a nommé sa colère. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois. Tu as soufflé. Bravo. Tu es venu vers maman. Je suis en colère. C'est dit. Les mains restent loin. C'est bien. Tu es venu vers l'adulte. Vers maman. Puis encore. Un peu d'eau brille sur les dalles. Le citron sent encore bon. Victorino range l'arrosoir ? Victorino pose l'arrosoir au soleil.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1739,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a nommé sa colère.
+narrateur|Mains loin.
+narrateur|Il peut s'éloigner.
+narrateur|Il rejoint maman, l'adulte.
+narrateur|Deux fois.
+maman|Tu as soufflé. Bravo.
+papa|Tu es venu vers maman.
+enfant-m|Je suis en colère. C'est dit.
+maman|Les mains restent loin. C'est bien.
+papa|Tu es venu vers l'adulte.
+enfant-m|Vers maman. Puis encore.
+narrateur|Un peu d'eau brille sur les dalles.
+narrateur|Le citron sent encore bon.
+maman|Victorino range l'arrosoir ?
+narrateur|Victorino pose l'arrosoir au soleil.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo repose un cube. Maman reste près de lui.</t>
+          <t>Aniss repose un cube. Maman reste près de lui. On laisse l'arrosoir au soleil ? Oui. L'eau va sécher. Tu as nommé. Tu t'es éloigné. Je suis plus calme. On va vers un adulte. C'est bien. On laisse le cube sur la table ? Oui. Il sent le pin. La porte du jardin reste ouverte. Le cube sent encore le pin. L'abeille est partie.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1921,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo repose un cube. Maman reste près de lui.</t>
+          <t>narrateur|Aniss repose un cube.
+narrateur|Maman reste près de lui.
+papa|On laisse l'arrosoir au soleil ?
+enfant-m|Oui. L'eau va sécher.
+maman|Tu as nommé. Tu t'es éloigné.
+enfant-m|Je suis plus calme.
+papa|On va vers un adulte. C'est bien.
+maman|On laisse le cube sur la table ?
+enfant-m|Oui. Il sent le pin.
+narrateur|La porte du jardin reste ouverte.
+narrateur|Le cube sent encore le pin.
+narrateur|L'abeille est partie.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais en colère. Je suis allé vers maman. Tes mains étaient loin. Bravo. Le jardin sentait le citron. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2100,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais en colère. Je suis allé vers maman.
+maman|Tes mains étaient loin. Bravo.
+papa|Le jardin sentait le citron.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo est dans la cuisine avec maman. Il empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Hugo sent son visage brûler. Ses mains deviennent chaudes et dures. Hugo dit : je suis en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Il ouvre les doigts. Il garde les mains loin. Hugo peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement. Hugo dit : maman, je suis en colère. La tour est tombée. Maman écoute. Hugo reste près d'elle. Plus tard, ils vont au jardin. Hugo arrose les fleurs. Un camarade renverse l'arrosoir. L'eau part. Hugo sent encore la chaleur. Il se souvient. Il dit : je suis en colère. Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle. Maman dit : tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un cube en bois sent le pin. La porte du jardin est ouverte. Un zeste de citron brille sur la table. Maman essuie une miette. Une abeille passe devant la porte. Le carrelage est un peu froid. Les cubes sont près du saladier. Aniss, tu empiles tout doux ? Oui. Une tour haute. En ce moment, Aniss empile des cubes. La tour est haute. Un cube glisse. La tour s'affaisse. Aniss sent son visage brûler. Ses mains deviennent chaudes. Je suis en colère. Il ouvre les doigts. Il garde les mains loin. Les mains restent loin. Aniss peut s'éloigner. Il s'éloigne de la table. Il va près de maman. Il souffle quatre fois, lentement. Maman, je suis en colère. Je t'écoute. La tour est tombée. Tu as nommé. Bravo. Aniss reste près d'elle. Plus tard, ils vont au jardin. Aniss arrose les fleurs. Victorino passe près des pots. L'arrosoir se renverse. L'eau part. Aniss sent encore la chaleur. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne. Il va vers maman, l'adulte. Il souffle. Tu as nommé. Tu as soufflé encore. Au jardin, tu as fait pareil. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte. Tu as soufflé à la table. Tu as soufflé au jardin. Deux fois. Mains loin. L'eau brille sur les dalles. Le citron sent encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La tour de Hugo s'affaisse. Que fait-il de sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tour d'Aniss s'affaisse. Que fait-il de sa colère ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1570,6 @@
 narrateur|Que fait-il de sa colère ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,7 +1599,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a nommé sa colère. Mains loin. Il peut s'éloigner. Il rejoint maman, l'adulte. Deux fois. Tu as soufflé. Bravo. Tu es venu vers maman. Je suis en colère. C'est dit. Les mains restent loin. C'est bien. Tu es venu vers l'adulte. Vers maman. Puis encore. Un peu d'eau brille sur les dalles. Le citron sent encore bon. Victorino range l'arrosoir ? Victorino pose l'arrosoir au soleil.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1790,7 +1789,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo repose un cube. Maman reste près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss repose un cube. Maman reste près de lui. On laisse l'arrosoir au soleil ? Oui. L'eau va sécher. Tu as nommé. Tu t'es éloigné. Je suis plus calme. On va vers un adulte. C'est bien. On laisse le cube sur la table ? Oui. Il sent le pin. La porte du jardin reste ouverte. Le cube sent encore le pin. L'abeille est partie.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1934,6 @@
 narrateur|L'abeille est partie.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais en colère. Je suis allé vers maman. Tes mains étaient loin. Bravo. Le jardin sentait le citron. L'histoire est finie.</t>
+          <t>J'étais en colère. Je suis allé vers maman. Tes mains étaient loin. Bravo. Le jardin sentait le citron.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais en colère. Je suis allé vers maman. Tes mains étaient loin. Bravo. Le jardin sentait le citron.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,11 +2100,9 @@
         <is>
           <t>enfant-m|J'étais en colère. Je suis allé vers maman.
 maman|Tes mains étaient loin. Bravo.
-papa|Le jardin sentait le citron.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Le jardin sentait le citron.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Aniss, Victorino, papa, maman</t>
         </is>
       </c>
     </row>
